--- a/Projects/Chapter2/sample-processing-plan.xlsx
+++ b/Projects/Chapter2/sample-processing-plan.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amysolman/Documents/GitHub/PhD/Projects/Chapter2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5CC34B7D-66D0-EF4D-B1F7-3BC5828F8033}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC611EB4-4C96-9A4E-A30D-5A5C031F2DE9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{7BB86048-1BEE-1644-9060-44F16CC62A7B}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
-    <sheet name="Additional" sheetId="2" r:id="rId3"/>
+    <sheet name="PMA" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Additional" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="151">
   <si>
     <t>Sample</t>
   </si>
@@ -185,9 +186,6 @@
     <t>NA</t>
   </si>
   <si>
-    <t>Sterile_Water</t>
-  </si>
-  <si>
     <t>Filtered_Volume_ml</t>
   </si>
   <si>
@@ -441,6 +439,48 @@
   </si>
   <si>
     <t>Length_3_cm</t>
+  </si>
+  <si>
+    <t>25.r2.b</t>
+  </si>
+  <si>
+    <t>250ml melt rather than 500ml</t>
+  </si>
+  <si>
+    <t>PMA NOTES</t>
+  </si>
+  <si>
+    <t>250ml melt water was filtered through the sample rather than 500ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Blank_6</t>
+  </si>
+  <si>
+    <t>Blank_7</t>
+  </si>
+  <si>
+    <t>ICPMS_SterileWater</t>
+  </si>
+  <si>
+    <t>IC_SterileWater</t>
+  </si>
+  <si>
+    <t>IC_MilliQ</t>
+  </si>
+  <si>
+    <t>ICPMS_MilliQ</t>
+  </si>
+  <si>
+    <t>Blank_8 MQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blank_9 MQ </t>
+  </si>
+  <si>
+    <t>Amplicon_Sterile_Water</t>
   </si>
 </sst>
 </file>
@@ -794,12 +834,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEBBFF7F-87E8-5D4A-98E3-0CF974F9EA3F}">
-  <dimension ref="A1:V54"/>
+  <dimension ref="A1:V58"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.1640625" bestFit="1" customWidth="1"/>
     <col min="8" max="10" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.83203125" bestFit="1" customWidth="1"/>
@@ -811,7 +852,7 @@
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -829,52 +870,52 @@
         <v>2</v>
       </c>
       <c r="G1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J1" t="s">
+        <v>136</v>
+      </c>
+      <c r="K1" t="s">
         <v>134</v>
-      </c>
-      <c r="I1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J1" t="s">
-        <v>137</v>
-      </c>
-      <c r="K1" t="s">
-        <v>135</v>
       </c>
       <c r="L1" t="s">
         <v>3</v>
       </c>
       <c r="M1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N1" t="s">
         <v>47</v>
       </c>
       <c r="O1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q1" t="s">
+        <v>58</v>
+      </c>
+      <c r="R1" t="s">
         <v>59</v>
-      </c>
-      <c r="R1" t="s">
-        <v>60</v>
       </c>
       <c r="S1" t="s">
         <v>4</v>
       </c>
       <c r="T1" t="s">
+        <v>130</v>
+      </c>
+      <c r="U1" t="s">
         <v>131</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>132</v>
-      </c>
-      <c r="V1" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.2">
@@ -882,7 +923,7 @@
         <v>44320</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
         <v>12</v>
@@ -922,13 +963,13 @@
         <v>3053</v>
       </c>
       <c r="Q2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.2">
@@ -936,7 +977,7 @@
         <v>44320</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
@@ -976,13 +1017,13 @@
         <v>51</v>
       </c>
       <c r="Q3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.2">
@@ -990,7 +1031,7 @@
         <v>44320</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
@@ -1030,13 +1071,13 @@
         <v>1665</v>
       </c>
       <c r="Q4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.2">
@@ -1044,7 +1085,7 @@
         <v>44320</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
@@ -1084,13 +1125,13 @@
         <v>51</v>
       </c>
       <c r="Q5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.2">
@@ -1098,7 +1139,7 @@
         <v>44320</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
         <v>14</v>
@@ -1138,13 +1179,13 @@
         <v>2666</v>
       </c>
       <c r="Q6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.2">
@@ -1152,7 +1193,7 @@
         <v>44320</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
@@ -1192,13 +1233,13 @@
         <v>51</v>
       </c>
       <c r="Q7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.2">
@@ -1206,7 +1247,7 @@
         <v>44320</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
         <v>15</v>
@@ -1246,13 +1287,13 @@
         <v>2671</v>
       </c>
       <c r="Q8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.2">
@@ -1260,7 +1301,7 @@
         <v>44320</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
         <v>15</v>
@@ -1300,13 +1341,13 @@
         <v>51</v>
       </c>
       <c r="Q9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.2">
@@ -1314,7 +1355,7 @@
         <v>44320</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
         <v>16</v>
@@ -1354,13 +1395,13 @@
         <v>2300</v>
       </c>
       <c r="Q10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.2">
@@ -1408,13 +1449,13 @@
         <v>51</v>
       </c>
       <c r="Q11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.2">
@@ -1462,13 +1503,13 @@
         <v>2929</v>
       </c>
       <c r="Q12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.2">
@@ -1516,13 +1557,13 @@
         <v>51</v>
       </c>
       <c r="Q13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.2">
@@ -1570,13 +1611,13 @@
         <v>2608</v>
       </c>
       <c r="Q14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.2">
@@ -1624,13 +1665,13 @@
         <v>51</v>
       </c>
       <c r="Q15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.2">
@@ -1678,13 +1719,13 @@
         <v>2021</v>
       </c>
       <c r="Q16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
@@ -1732,13 +1773,13 @@
         <v>51</v>
       </c>
       <c r="Q17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.2">
@@ -1786,13 +1827,13 @@
         <v>2673</v>
       </c>
       <c r="Q18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.2">
@@ -1840,13 +1881,13 @@
         <v>1106</v>
       </c>
       <c r="Q19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.2">
@@ -1900,13 +1941,13 @@
         <v>2689</v>
       </c>
       <c r="Q20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.2">
@@ -1954,13 +1995,13 @@
         <v>1313</v>
       </c>
       <c r="Q21" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S21" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.2">
@@ -2014,13 +2055,13 @@
         <v>2954</v>
       </c>
       <c r="Q22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.2">
@@ -2068,13 +2109,13 @@
         <v>1411</v>
       </c>
       <c r="Q23" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S23" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.2">
@@ -2128,13 +2169,13 @@
         <v>3642</v>
       </c>
       <c r="Q24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.2">
@@ -2182,13 +2223,13 @@
         <v>1328</v>
       </c>
       <c r="Q25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R25" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.2">
@@ -2208,7 +2249,7 @@
         <v>51</v>
       </c>
       <c r="F26" t="s">
-        <v>52</v>
+        <v>150</v>
       </c>
       <c r="G26">
         <v>200</v>
@@ -2217,7 +2258,7 @@
         <v>51</v>
       </c>
       <c r="L26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M26" t="s">
         <v>51</v>
@@ -2235,10 +2276,10 @@
         <v>51</v>
       </c>
       <c r="R26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.2">
@@ -2258,7 +2299,7 @@
         <v>51</v>
       </c>
       <c r="F27" t="s">
-        <v>52</v>
+        <v>150</v>
       </c>
       <c r="G27">
         <v>200</v>
@@ -2267,7 +2308,7 @@
         <v>51</v>
       </c>
       <c r="L27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M27" t="s">
         <v>51</v>
@@ -2285,10 +2326,10 @@
         <v>51</v>
       </c>
       <c r="R27" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S27" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.2">
@@ -2308,7 +2349,7 @@
         <v>51</v>
       </c>
       <c r="F28" t="s">
-        <v>52</v>
+        <v>150</v>
       </c>
       <c r="G28">
         <v>200</v>
@@ -2317,7 +2358,7 @@
         <v>51</v>
       </c>
       <c r="L28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M28" t="s">
         <v>51</v>
@@ -2335,10 +2376,10 @@
         <v>51</v>
       </c>
       <c r="R28" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S28" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.2">
@@ -2392,13 +2433,13 @@
         <v>1674</v>
       </c>
       <c r="Q29" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S29" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.2">
@@ -2446,13 +2487,13 @@
         <v>894</v>
       </c>
       <c r="Q30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.2">
@@ -2506,13 +2547,13 @@
         <v>2133</v>
       </c>
       <c r="Q31" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S31" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.2">
@@ -2560,13 +2601,13 @@
         <v>800</v>
       </c>
       <c r="Q32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R32" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.2">
@@ -2620,13 +2661,13 @@
         <v>2811</v>
       </c>
       <c r="Q33" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R33" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S33" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.2">
@@ -2674,13 +2715,13 @@
         <v>928</v>
       </c>
       <c r="Q34" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S34" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.2">
@@ -2691,7 +2732,7 @@
         <v>45</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D35" s="2">
         <v>78.141909999999996</v>
@@ -2734,13 +2775,13 @@
         <v>2180</v>
       </c>
       <c r="Q35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.2">
@@ -2748,10 +2789,10 @@
         <v>44322</v>
       </c>
       <c r="B36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D36" s="2">
         <v>78.141909999999996</v>
@@ -2787,13 +2828,13 @@
         <v>1088</v>
       </c>
       <c r="Q36" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R36" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S36" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.2">
@@ -2801,10 +2842,10 @@
         <v>44322</v>
       </c>
       <c r="B37" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D37" s="2">
         <v>78.144490000000005</v>
@@ -2847,13 +2888,13 @@
         <v>2696</v>
       </c>
       <c r="Q37" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R37" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S37" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.2">
@@ -2861,10 +2902,10 @@
         <v>44322</v>
       </c>
       <c r="B38" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D38" s="2">
         <v>78.144490000000005</v>
@@ -2900,13 +2941,13 @@
         <v>1018</v>
       </c>
       <c r="Q38" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S38" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.2">
@@ -2914,10 +2955,10 @@
         <v>44322</v>
       </c>
       <c r="B39" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D39" s="2">
         <v>78.144630000000006</v>
@@ -2960,13 +3001,13 @@
         <v>3106</v>
       </c>
       <c r="Q39" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R39" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S39" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.2">
@@ -2974,10 +3015,10 @@
         <v>44322</v>
       </c>
       <c r="B40" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D40" s="2">
         <v>78.144630000000006</v>
@@ -3013,13 +3054,13 @@
         <v>1049</v>
       </c>
       <c r="Q40" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R40" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S40" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.2">
@@ -3027,10 +3068,10 @@
         <v>44323</v>
       </c>
       <c r="B41" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D41" s="2">
         <v>78.130120000000005</v>
@@ -3039,7 +3080,13 @@
         <v>16.16281</v>
       </c>
       <c r="L41" t="s">
-        <v>117</v>
+        <v>116</v>
+      </c>
+      <c r="N41">
+        <v>6.82</v>
+      </c>
+      <c r="O41">
+        <v>7.8</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.2">
@@ -3047,10 +3094,10 @@
         <v>44323</v>
       </c>
       <c r="B42" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D42" s="2">
         <v>78.130120000000005</v>
@@ -3059,7 +3106,13 @@
         <v>16.16281</v>
       </c>
       <c r="L42" t="s">
-        <v>117</v>
+        <v>116</v>
+      </c>
+      <c r="N42">
+        <v>6.04</v>
+      </c>
+      <c r="O42">
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.2">
@@ -3067,10 +3120,10 @@
         <v>44323</v>
       </c>
       <c r="B43" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D43" s="2">
         <v>78.130120000000005</v>
@@ -3079,7 +3132,13 @@
         <v>16.164999999999999</v>
       </c>
       <c r="L43" t="s">
-        <v>117</v>
+        <v>116</v>
+      </c>
+      <c r="N43">
+        <v>7.85</v>
+      </c>
+      <c r="O43">
+        <v>10.5</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.2">
@@ -3087,10 +3146,10 @@
         <v>44323</v>
       </c>
       <c r="B44" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D44" s="2">
         <v>78.130120000000005</v>
@@ -3099,7 +3158,13 @@
         <v>16.164999999999999</v>
       </c>
       <c r="L44" t="s">
-        <v>117</v>
+        <v>116</v>
+      </c>
+      <c r="N44">
+        <v>6.45</v>
+      </c>
+      <c r="O44">
+        <v>11.3</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.2">
@@ -3107,10 +3172,10 @@
         <v>44323</v>
       </c>
       <c r="B45" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D45" s="2">
         <v>78.128280000000004</v>
@@ -3119,7 +3184,16 @@
         <v>16.163730000000001</v>
       </c>
       <c r="L45" t="s">
-        <v>117</v>
+        <v>116</v>
+      </c>
+      <c r="N45">
+        <v>6.7</v>
+      </c>
+      <c r="O45">
+        <v>5.4</v>
+      </c>
+      <c r="P45" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.2">
@@ -3127,10 +3201,10 @@
         <v>44323</v>
       </c>
       <c r="B46" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D46" s="2">
         <v>78.128280000000004</v>
@@ -3139,7 +3213,13 @@
         <v>16.163730000000001</v>
       </c>
       <c r="L46" t="s">
-        <v>117</v>
+        <v>116</v>
+      </c>
+      <c r="N46">
+        <v>8.06</v>
+      </c>
+      <c r="O46">
+        <v>2.7</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.2">
@@ -3147,10 +3227,10 @@
         <v>44323</v>
       </c>
       <c r="B47" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D47" s="2">
         <v>78.128399999999999</v>
@@ -3159,7 +3239,13 @@
         <v>16.16582</v>
       </c>
       <c r="L47" t="s">
-        <v>117</v>
+        <v>116</v>
+      </c>
+      <c r="N47">
+        <v>6.78</v>
+      </c>
+      <c r="O47">
+        <v>5.5</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.2">
@@ -3167,10 +3253,10 @@
         <v>44323</v>
       </c>
       <c r="B48" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D48" s="2">
         <v>78.128399999999999</v>
@@ -3179,18 +3265,24 @@
         <v>16.16582</v>
       </c>
       <c r="L48" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+      <c r="N48">
+        <v>6.84</v>
+      </c>
+      <c r="O48">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>44323</v>
       </c>
       <c r="B49" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D49" s="2">
         <v>78.126630000000006</v>
@@ -3199,18 +3291,24 @@
         <v>16.167549999999999</v>
       </c>
       <c r="L49" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+      <c r="N49">
+        <v>6.74</v>
+      </c>
+      <c r="O49">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>44323</v>
       </c>
       <c r="B50" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D50" s="2">
         <v>78.126630000000006</v>
@@ -3219,18 +3317,24 @@
         <v>16.167549999999999</v>
       </c>
       <c r="L50" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+      <c r="N50">
+        <v>6.53</v>
+      </c>
+      <c r="O50">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>44323</v>
       </c>
       <c r="B51" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D51" s="2">
         <v>78.126829999999998</v>
@@ -3239,18 +3343,24 @@
         <v>16.169699999999999</v>
       </c>
       <c r="L51" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+      <c r="N51">
+        <v>6.86</v>
+      </c>
+      <c r="O51">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>44323</v>
       </c>
       <c r="B52" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D52" s="2">
         <v>78.126829999999998</v>
@@ -3259,15 +3369,21 @@
         <v>16.169699999999999</v>
       </c>
       <c r="L52" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+      <c r="N52">
+        <v>6.71</v>
+      </c>
+      <c r="O52">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>44322</v>
       </c>
       <c r="B53" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>51</v>
@@ -3279,18 +3395,18 @@
         <v>51</v>
       </c>
       <c r="F53" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L53" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>44322</v>
       </c>
       <c r="B54" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>51</v>
@@ -3302,10 +3418,42 @@
         <v>51</v>
       </c>
       <c r="F54" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L54" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B55" t="s">
+        <v>142</v>
+      </c>
+      <c r="F55" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B56" t="s">
+        <v>143</v>
+      </c>
+      <c r="F56" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B57" t="s">
+        <v>148</v>
+      </c>
+      <c r="F57" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B58" t="s">
+        <v>149</v>
+      </c>
+      <c r="F58" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -3314,6 +3462,35 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F084A1F0-4259-2240-9538-78396171068F}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="26.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C03269F1-38C9-D04B-916C-5B03CAC4301E}">
   <dimension ref="A1:O44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -3329,34 +3506,34 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1" t="s">
         <v>86</v>
-      </c>
-      <c r="H1" t="s">
-        <v>87</v>
       </c>
       <c r="K1" t="s">
         <v>47</v>
       </c>
       <c r="L1" t="s">
+        <v>87</v>
+      </c>
+      <c r="M1" t="s">
         <v>88</v>
       </c>
-      <c r="M1" t="s">
-        <v>89</v>
-      </c>
       <c r="N1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
@@ -3364,7 +3541,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
         <v>51</v>
@@ -3388,7 +3565,7 @@
         <v>51</v>
       </c>
       <c r="O2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
@@ -3396,7 +3573,7 @@
         <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
         <v>51</v>
@@ -3420,7 +3597,7 @@
         <v>51</v>
       </c>
       <c r="O3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
@@ -3428,7 +3605,7 @@
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s">
         <v>43</v>
@@ -3454,7 +3631,7 @@
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C5" t="s">
         <v>44</v>
@@ -3480,7 +3657,7 @@
         <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s">
         <v>43</v>
@@ -3506,7 +3683,7 @@
         <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C7" t="s">
         <v>44</v>
@@ -3529,10 +3706,10 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s">
         <v>43</v>
@@ -3555,10 +3732,10 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="s">
         <v>44</v>
@@ -3581,10 +3758,10 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C10" t="s">
         <v>43</v>
@@ -3607,10 +3784,10 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C11" t="s">
         <v>44</v>
@@ -3633,10 +3810,10 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C12" t="s">
         <v>43</v>
@@ -3659,10 +3836,10 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C13" t="s">
         <v>44</v>
@@ -3685,10 +3862,10 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C14" t="s">
         <v>43</v>
@@ -3696,10 +3873,10 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C15" t="s">
         <v>43</v>
@@ -3707,10 +3884,10 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
         <v>43</v>
@@ -3718,10 +3895,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C17" t="s">
         <v>43</v>
@@ -3729,37 +3906,37 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E20" t="s">
+        <v>109</v>
+      </c>
+      <c r="F20" t="s">
         <v>110</v>
       </c>
-      <c r="F20" t="s">
-        <v>111</v>
-      </c>
       <c r="G20" t="s">
+        <v>106</v>
+      </c>
+      <c r="H20" t="s">
+        <v>105</v>
+      </c>
+      <c r="I20" t="s">
         <v>107</v>
       </c>
-      <c r="H20" t="s">
-        <v>106</v>
-      </c>
-      <c r="I20" t="s">
+      <c r="J20" t="s">
+        <v>69</v>
+      </c>
+      <c r="K20" t="s">
+        <v>87</v>
+      </c>
+      <c r="L20" t="s">
+        <v>58</v>
+      </c>
+      <c r="M20" t="s">
+        <v>59</v>
+      </c>
+      <c r="N20" t="s">
         <v>108</v>
-      </c>
-      <c r="J20" t="s">
-        <v>70</v>
-      </c>
-      <c r="K20" t="s">
-        <v>88</v>
-      </c>
-      <c r="L20" t="s">
-        <v>59</v>
-      </c>
-      <c r="M20" t="s">
-        <v>60</v>
-      </c>
-      <c r="N20" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
@@ -3773,7 +3950,7 @@
         <v>43</v>
       </c>
       <c r="D21" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L21" t="s">
         <v>51</v>
@@ -3790,7 +3967,7 @@
         <v>43</v>
       </c>
       <c r="D22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G22" t="s">
         <v>51</v>
@@ -3825,7 +4002,7 @@
         <v>44</v>
       </c>
       <c r="D23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L23" t="s">
         <v>51</v>
@@ -3842,7 +4019,7 @@
         <v>44</v>
       </c>
       <c r="D24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G24" t="s">
         <v>51</v>
@@ -3877,7 +4054,7 @@
         <v>43</v>
       </c>
       <c r="D25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L25" t="s">
         <v>51</v>
@@ -3894,7 +4071,7 @@
         <v>43</v>
       </c>
       <c r="D26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G26" t="s">
         <v>51</v>
@@ -3929,7 +4106,7 @@
         <v>44</v>
       </c>
       <c r="D27" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L27" t="s">
         <v>51</v>
@@ -3946,7 +4123,7 @@
         <v>44</v>
       </c>
       <c r="D28" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G28" t="s">
         <v>51</v>
@@ -3981,7 +4158,7 @@
         <v>43</v>
       </c>
       <c r="D29" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L29" t="s">
         <v>51</v>
@@ -3998,7 +4175,7 @@
         <v>43</v>
       </c>
       <c r="D30" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G30" t="s">
         <v>51</v>
@@ -4033,7 +4210,7 @@
         <v>44</v>
       </c>
       <c r="D31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L31" t="s">
         <v>51</v>
@@ -4050,7 +4227,7 @@
         <v>44</v>
       </c>
       <c r="D32" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G32" t="s">
         <v>51</v>
@@ -4076,7 +4253,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B33" t="s">
         <v>45</v>
@@ -4085,7 +4262,7 @@
         <v>43</v>
       </c>
       <c r="D33" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L33" t="s">
         <v>51</v>
@@ -4093,7 +4270,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B34" t="s">
         <v>45</v>
@@ -4102,7 +4279,7 @@
         <v>43</v>
       </c>
       <c r="D34" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G34" t="s">
         <v>51</v>
@@ -4128,16 +4305,16 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B35" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C35" t="s">
         <v>44</v>
       </c>
       <c r="D35" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L35" t="s">
         <v>51</v>
@@ -4145,16 +4322,16 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C36" t="s">
         <v>44</v>
       </c>
       <c r="D36" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G36" t="s">
         <v>51</v>
@@ -4180,31 +4357,31 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B37" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C37" t="s">
         <v>43</v>
       </c>
       <c r="D37" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E37" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F37" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G37" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J37">
         <v>2696</v>
       </c>
       <c r="K37" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L37" t="s">
         <v>51</v>
@@ -4212,16 +4389,16 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B38" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C38" t="s">
         <v>43</v>
       </c>
       <c r="D38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G38" t="s">
         <v>51</v>
@@ -4247,16 +4424,16 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B39" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C39" t="s">
         <v>44</v>
       </c>
       <c r="D39" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L39" t="s">
         <v>51</v>
@@ -4264,16 +4441,16 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B40" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C40" t="s">
         <v>44</v>
       </c>
       <c r="D40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G40" t="s">
         <v>51</v>
@@ -4299,28 +4476,28 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B41" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C41" t="s">
         <v>43</v>
       </c>
       <c r="D41" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E41" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F41" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G41" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K41" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L41" t="s">
         <v>51</v>
@@ -4328,16 +4505,16 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B42" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C42" t="s">
         <v>43</v>
       </c>
       <c r="D42" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G42" t="s">
         <v>51</v>
@@ -4363,16 +4540,16 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B43" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C43" t="s">
         <v>44</v>
       </c>
       <c r="D43" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J43">
         <v>3106</v>
@@ -4383,16 +4560,16 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B44" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C44" t="s">
         <v>44</v>
       </c>
       <c r="D44" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G44" t="s">
         <v>51</v>
@@ -4421,7 +4598,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{128BBBF5-7C1D-B948-8CE0-1627DC18E553}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -4432,18 +4609,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" t="s">
         <v>57</v>
-      </c>
-      <c r="B1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" t="s">
         <v>71</v>
-      </c>
-      <c r="B2" t="s">
-        <v>72</v>
       </c>
     </row>
   </sheetData>
